--- a/artfynd/A 23933-2026 artfynd.xlsx
+++ b/artfynd/A 23933-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134680429</v>
+        <v>134697837</v>
       </c>
       <c r="B2" t="n">
-        <v>97853</v>
+        <v>96586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1590</v>
+        <v>815</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dunmossa</t>
+          <t>Stor skogsbäckmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trichocolea tomentella</t>
+          <t>Pseudohygrohypnum subeugyrium</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ehrh.) Dumort.</t>
+          <t>(Renauld &amp; Cardot) Ignatov &amp; Ignatova</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>345045</v>
+        <v>345141</v>
       </c>
       <c r="R2" t="n">
-        <v>6533040</v>
+        <v>6533227</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -759,7 +759,12 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>Källpåverkad mark vid bäck.</t>
+          <t>Bäck, nedskuren i terrängen.</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>På sten i och vid bäcken.</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -777,32 +782,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134680431</v>
+        <v>134697839</v>
       </c>
       <c r="B3" t="n">
-        <v>97853</v>
+        <v>96586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1590</v>
+        <v>815</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dunmossa</t>
+          <t>Stor skogsbäckmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Trichocolea tomentella</t>
+          <t>Pseudohygrohypnum subeugyrium</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ehrh.) Dumort.</t>
+          <t>(Renauld &amp; Cardot) Ignatov &amp; Ignatova</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -812,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>345059</v>
+        <v>345145</v>
       </c>
       <c r="R3" t="n">
-        <v>6533053</v>
+        <v>6533256</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -837,7 +842,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>Tisselskog</t>
+          <t>Steneby</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -861,7 +866,12 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Källpåverkad mark vid bäck.</t>
+          <t>Bäck, nedskuren i terrängen.</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>På sten i och vid bäcken.</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
@@ -879,45 +889,50 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134681153</v>
+        <v>134698673</v>
       </c>
       <c r="B4" t="n">
-        <v>97873</v>
+        <v>96586</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2609</v>
+        <v>815</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Blåsfliksmossa</t>
+          <t>Stor skogsbäckmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lejeunea cavifolia</t>
+          <t>Pseudohygrohypnum subeugyrium</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ehrh.) Lindb.</t>
+          <t>(Renauld &amp; Cardot) Ignatov &amp; Ignatova</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>”Skårdalsbäcken” (bäck N om Skårdalen som mynnar i Råvarpen), Dls</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>345145</v>
+        <v>345068</v>
       </c>
       <c r="R4" t="n">
-        <v>6533256</v>
+        <v>6533103</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -968,7 +983,7 @@
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>På sten i och vid bäcken.</t>
+          <t>På sten i bäcken.</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -986,45 +1001,53 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134681129</v>
+        <v>134704128</v>
       </c>
       <c r="B5" t="n">
-        <v>96279</v>
+        <v>96586</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2774</v>
+        <v>815</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Källgräsmossa</t>
+          <t>Stor skogsbäckmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Brachythecium rivulare</t>
+          <t>Pseudohygrohypnum subeugyrium</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Schimp.</t>
+          <t>(Renauld &amp; Cardot) Ignatov &amp; Ignatova</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>”Skårdalsbäcken” (bäck N om Skårdalen som mynnar i Råvarpen), Dls</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>345142</v>
+        <v>345128</v>
       </c>
       <c r="R5" t="n">
-        <v>6533266</v>
+        <v>6533208</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1065,17 +1088,18 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Bäck, nedskuren i terrängen.</t>
+          <t>Skogsbäck.</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>Litet bäckdråg vid sidan av bäcken.</t>
+          <t>På stenar i bäcken.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1093,45 +1117,49 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134680675</v>
+        <v>134704137</v>
       </c>
       <c r="B6" t="n">
-        <v>96410</v>
+        <v>96586</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2812</v>
+        <v>815</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kransmossa</t>
+          <t>Stor skogsbäckmossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hylocomiadelphus triquetrus</t>
+          <t>Pseudohygrohypnum subeugyrium</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Hedw.) Ochyra &amp; Stebel</t>
+          <t>(Renauld &amp; Cardot) Ignatov &amp; Ignatova</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>”Skårdalsbäcken” (bäck N om Skårdalen som mynnar i Råvarpen), Dls</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>345150</v>
+        <v>345094</v>
       </c>
       <c r="R6" t="n">
-        <v>6533260</v>
+        <v>6533138</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1172,8 +1200,19 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Skogsbäck.</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>På stenar i bäcken.</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1190,32 +1229,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134680678</v>
+        <v>134680429</v>
       </c>
       <c r="B7" t="n">
-        <v>96533</v>
+        <v>97853</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2818</v>
+        <v>1590</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1264,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>345150</v>
+        <v>345045</v>
       </c>
       <c r="R7" t="n">
-        <v>6533260</v>
+        <v>6533040</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1271,6 +1310,11 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Källpåverkad mark vid bäck.</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1287,10 +1331,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134681282</v>
+        <v>134680431</v>
       </c>
       <c r="B8" t="n">
-        <v>57391</v>
+        <v>97853</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1298,21 +1342,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102961</v>
+        <v>1590</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Drillsnäppa</t>
+          <t>Dunmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Actitis hypoleucos</t>
+          <t>Trichocolea tomentella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ehrh.) Dumort.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1322,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>345188</v>
+        <v>345059</v>
       </c>
       <c r="R8" t="n">
-        <v>6533341</v>
+        <v>6533053</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1347,7 +1391,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>Steneby</t>
+          <t>Tisselskog</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
@@ -1368,6 +1412,11 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Källpåverkad mark vid bäck.</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1384,32 +1433,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134681280</v>
+        <v>134681153</v>
       </c>
       <c r="B9" t="n">
-        <v>106894</v>
+        <v>97873</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220785</v>
+        <v>2609</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåsfliksmossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lejeunea cavifolia</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ehrh.) Lindb.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1419,10 +1468,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>345177</v>
+        <v>345145</v>
       </c>
       <c r="R9" t="n">
-        <v>6533320</v>
+        <v>6533256</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1465,6 +1514,16 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Bäck, nedskuren i terrängen.</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>På sten i och vid bäcken.</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1481,32 +1540,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134681283</v>
+        <v>134681129</v>
       </c>
       <c r="B10" t="n">
-        <v>106894</v>
+        <v>96279</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220785</v>
+        <v>2774</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Källgräsmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Brachythecium rivulare</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schimp.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1516,10 +1575,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>345188</v>
+        <v>345142</v>
       </c>
       <c r="R10" t="n">
-        <v>6533341</v>
+        <v>6533266</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1562,6 +1621,16 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Bäck, nedskuren i terrängen.</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>Litet bäckdråg vid sidan av bäcken.</t>
+        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
@@ -1578,10 +1647,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134680674</v>
+        <v>134680675</v>
       </c>
       <c r="B11" t="n">
-        <v>101403</v>
+        <v>96410</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1658,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>222498</v>
+        <v>2812</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kransmossa</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Hylocomiadelphus triquetrus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) Ochyra &amp; Stebel</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1675,10 +1744,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134681167</v>
+        <v>134680678</v>
       </c>
       <c r="B12" t="n">
-        <v>101305</v>
+        <v>96533</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1686,21 +1755,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222771</v>
+        <v>2818</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1710,10 +1779,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>345145</v>
+        <v>345150</v>
       </c>
       <c r="R12" t="n">
-        <v>6533256</v>
+        <v>6533260</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1735,7 +1804,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>Steneby</t>
+          <t>Tisselskog</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
@@ -1756,11 +1825,6 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>Vid bäck, nedskuren i terrängen.</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1777,32 +1841,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134681279</v>
+        <v>134681282</v>
       </c>
       <c r="B13" t="n">
-        <v>101305</v>
+        <v>57391</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222771</v>
+        <v>102961</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Drillsnäppa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Actitis hypoleucos</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1812,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>345177</v>
+        <v>345188</v>
       </c>
       <c r="R13" t="n">
-        <v>6533320</v>
+        <v>6533341</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1874,27 +1938,27 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134681139</v>
+        <v>134681280</v>
       </c>
       <c r="B14" t="n">
-        <v>101324</v>
+        <v>106894</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222782</v>
+        <v>220785</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitsippa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Anemone nemorosa</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1909,10 +1973,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>345145</v>
+        <v>345177</v>
       </c>
       <c r="R14" t="n">
-        <v>6533256</v>
+        <v>6533320</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1955,11 +2019,6 @@
       </c>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>Vid bäck, nedskuren i terrängen.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -1976,32 +2035,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134681140</v>
+        <v>134681283</v>
       </c>
       <c r="B15" t="n">
-        <v>98249</v>
+        <v>106894</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223358</v>
+        <v>220785</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Hultbräken</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Phegopteris connectilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Michx.) Watt</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2011,10 +2070,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>345145</v>
+        <v>345188</v>
       </c>
       <c r="R15" t="n">
-        <v>6533256</v>
+        <v>6533341</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2058,11 +2117,6 @@
       <c r="AG15" t="b">
         <v>0</v>
       </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>Vid bäck, nedskuren i terrängen.</t>
-        </is>
-      </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
@@ -2075,6 +2129,827 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>134700169</v>
+      </c>
+      <c r="B16" t="n">
+        <v>106894</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>”Skårdalsbäcken” (bäck N om Skårdalen som mynnar i Råvarpen), Dls</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>345079</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6533103</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Småträd och plantor.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Granskog, med lövinslag längs bäck.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>134700234</v>
+      </c>
+      <c r="B17" t="n">
+        <v>106894</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>”Skårdalsbäcken” (bäck N om Skårdalen som mynnar i Råvarpen), Dls</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>345063</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6533062</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Minst ett träd + småplantor.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Något källpåverkad mark.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>134699491</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99960</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>222364</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Skärmstarr</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carex remota</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>”Skårdalsbäcken” (bäck N om Skårdalen som mynnar i Råvarpen), Dls</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>345145</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6533256</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Bäck, nedskuren i terrängen.</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>Bäckkant.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>134680674</v>
+      </c>
+      <c r="B19" t="n">
+        <v>101403</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>”Skårdalsbäcken” (bäck N om Skårdalen som mynnar i Råvarpen), Dls</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>345150</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6533260</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tisselskog</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>134681167</v>
+      </c>
+      <c r="B20" t="n">
+        <v>101305</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>”Skårdalsbäcken” (bäck N om Skårdalen som mynnar i Råvarpen), Dls</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>345145</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6533256</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Vid bäck, nedskuren i terrängen.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>134681279</v>
+      </c>
+      <c r="B21" t="n">
+        <v>101305</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>”Skårdalsbäcken” (bäck N om Skårdalen som mynnar i Råvarpen), Dls</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>345177</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6533320</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>134681139</v>
+      </c>
+      <c r="B22" t="n">
+        <v>101324</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>222782</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Vitsippa</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Anemone nemorosa</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>”Skårdalsbäcken” (bäck N om Skårdalen som mynnar i Råvarpen), Dls</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>345145</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6533256</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Vid bäck, nedskuren i terrängen.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>134681140</v>
+      </c>
+      <c r="B23" t="n">
+        <v>98249</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>223358</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Hultbräken</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Phegopteris connectilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Michx.) Watt</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>”Skårdalsbäcken” (bäck N om Skårdalen som mynnar i Råvarpen), Dls</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>345145</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6533256</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Bengtsfors</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalsland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Steneby</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Vid bäck, nedskuren i terrängen.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Leif Appelgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 23933-2026 artfynd.xlsx
+++ b/artfynd/A 23933-2026 artfynd.xlsx
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>345059</v>
+        <v>345058</v>
       </c>
       <c r="R8" t="n">
-        <v>6533053</v>
+        <v>6533054</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1876,10 +1876,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>345188</v>
+        <v>345195</v>
       </c>
       <c r="R13" t="n">
-        <v>6533341</v>
+        <v>6533338</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1973,7 +1973,7 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>345177</v>
+        <v>345180</v>
       </c>
       <c r="R14" t="n">
         <v>6533320</v>
@@ -1998,7 +1998,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>Steneby</t>
+          <t>Tisselskog</t>
         </is>
       </c>
       <c r="Y14" t="inlineStr">
@@ -2070,10 +2070,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>345188</v>
+        <v>345195</v>
       </c>
       <c r="R15" t="n">
-        <v>6533341</v>
+        <v>6533338</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>345177</v>
+        <v>345180</v>
       </c>
       <c r="R21" t="n">
         <v>6533320</v>
@@ -2712,7 +2712,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>Steneby</t>
+          <t>Tisselskog</t>
         </is>
       </c>
       <c r="Y21" t="inlineStr">

--- a/artfynd/A 23933-2026 artfynd.xlsx
+++ b/artfynd/A 23933-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134697837</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -886,6 +896,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134697839</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -998,6 +1013,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134698673</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1114,6 +1134,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704128</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1226,6 +1251,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134704137</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1328,6 +1358,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134680429</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1430,6 +1465,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134680431</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1537,6 +1577,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134681153</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1644,6 +1689,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134681129</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1741,6 +1791,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134680675</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1838,6 +1893,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134680678</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1935,6 +1995,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134681282</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2032,6 +2097,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134681280</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2129,6 +2199,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134681283</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2236,6 +2311,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134700169</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2343,6 +2423,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134700234</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2450,6 +2535,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134699491</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2547,6 +2637,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134680674</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2649,6 +2744,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134681167</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2746,6 +2846,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134681279</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2848,6 +2953,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134681139</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2950,8 +3060,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134681140</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>